--- a/c.输出/论文数据.xlsx
+++ b/c.输出/论文数据.xlsx
@@ -827,7 +827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -858,26 +858,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1201,10 +1183,10 @@
   <cols>
     <col min="1" max="1" width="11" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.5916666666667" style="7" customWidth="1"/>
-    <col min="3" max="3" width="11.15" style="7" customWidth="1"/>
+    <col min="3" max="3" width="16.725" style="7" customWidth="1"/>
     <col min="4" max="4" width="8.75" style="7" customWidth="1"/>
     <col min="5" max="5" width="14.7083333333333" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.8583333333333" style="7" customWidth="1"/>
+    <col min="6" max="6" width="17.6833333333333" style="7" customWidth="1"/>
     <col min="7" max="10" width="12.625" style="6"/>
     <col min="11" max="16384" width="9" style="6"/>
   </cols>
@@ -1232,1871 +1214,1866 @@
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="13"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="10"/>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="11"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="10"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="13"/>
+      <c r="F7" s="11"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11">
         <v>5</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>5</v>
       </c>
-      <c r="E9" s="13">
-        <v>1</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="11">
+        <v>1</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0</v>
+      </c>
+      <c r="D15" s="11">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="11">
+        <v>2</v>
+      </c>
+      <c r="C16" s="11">
+        <v>0</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0</v>
+      </c>
+      <c r="E16" s="11">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13" t="s">
+      <c r="C17" s="11">
+        <v>0</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="11">
+        <v>4</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="11">
+        <v>5</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <v>0</v>
+      </c>
+      <c r="F19" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="11">
+        <v>6</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0</v>
+      </c>
+      <c r="D20" s="11">
+        <v>0</v>
+      </c>
+      <c r="E20" s="11">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="11">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11">
+        <v>0</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="11">
+        <v>8</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="11">
+        <v>9</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="11">
+        <v>10</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0</v>
+      </c>
+      <c r="D24" s="11">
+        <v>0</v>
+      </c>
+      <c r="E24" s="11">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="11">
+        <v>11</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0</v>
+      </c>
+      <c r="D25" s="11">
+        <v>0</v>
+      </c>
+      <c r="E25" s="11">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="11">
+        <v>12</v>
+      </c>
+      <c r="C26" s="11">
+        <v>0</v>
+      </c>
+      <c r="D26" s="11">
+        <v>0</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="11">
+        <v>13</v>
+      </c>
+      <c r="C27" s="11">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11">
+        <v>0</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="11">
+        <v>14</v>
+      </c>
+      <c r="C28" s="11">
+        <v>0</v>
+      </c>
+      <c r="D28" s="11">
+        <v>0</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="11">
+        <v>15</v>
+      </c>
+      <c r="C29" s="11">
+        <v>0</v>
+      </c>
+      <c r="D29" s="11">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="11">
+        <v>16</v>
+      </c>
+      <c r="C30" s="11">
+        <v>0</v>
+      </c>
+      <c r="D30" s="11">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="11">
+        <v>17</v>
+      </c>
+      <c r="C31" s="11">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="11">
+        <v>18</v>
+      </c>
+      <c r="C32" s="11">
+        <v>0</v>
+      </c>
+      <c r="D32" s="11">
+        <v>0</v>
+      </c>
+      <c r="E32" s="11">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="11">
+        <v>19</v>
+      </c>
+      <c r="C33" s="11">
+        <v>0</v>
+      </c>
+      <c r="D33" s="11">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11">
+        <v>0</v>
+      </c>
+      <c r="F33" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="11">
         <v>20</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="C34" s="11">
+        <v>0</v>
+      </c>
+      <c r="D34" s="11">
+        <v>0</v>
+      </c>
+      <c r="E34" s="11">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="11">
         <v>21</v>
       </c>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13">
-        <v>1</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" s="14"/>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="15" t="s">
+      <c r="C35" s="11">
+        <v>0</v>
+      </c>
+      <c r="D35" s="11">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="11">
         <v>22</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="16" t="s">
+      <c r="C36" s="11">
+        <v>0</v>
+      </c>
+      <c r="D36" s="11">
+        <v>0</v>
+      </c>
+      <c r="E36" s="11">
+        <v>0</v>
+      </c>
+      <c r="F36" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="11">
         <v>23</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C37" s="11">
+        <v>0</v>
+      </c>
+      <c r="D37" s="11">
+        <v>0</v>
+      </c>
+      <c r="E37" s="11">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="11">
         <v>24</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="C38" s="11">
+        <v>0</v>
+      </c>
+      <c r="D38" s="11">
+        <v>0</v>
+      </c>
+      <c r="E38" s="11">
+        <v>0</v>
+      </c>
+      <c r="F38" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="11">
         <v>25</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="C39" s="11">
+        <v>0</v>
+      </c>
+      <c r="D39" s="11">
+        <v>0</v>
+      </c>
+      <c r="E39" s="11">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="11">
         <v>26</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="C40" s="11">
+        <v>0</v>
+      </c>
+      <c r="D40" s="11">
+        <v>0</v>
+      </c>
+      <c r="E40" s="11">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="11">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" s="17">
-        <v>1</v>
-      </c>
-      <c r="C15" s="17">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="17">
-        <v>2</v>
-      </c>
-      <c r="C16" s="17">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="17">
-        <v>3</v>
-      </c>
-      <c r="C17" s="17">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="17">
-        <v>4</v>
-      </c>
-      <c r="C18" s="17">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="17">
-        <v>5</v>
-      </c>
-      <c r="C19" s="17">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="17">
-        <v>6</v>
-      </c>
-      <c r="C20" s="17">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
-        <v>0</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="17">
-        <v>7</v>
-      </c>
-      <c r="C21" s="17">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="17">
-        <v>8</v>
-      </c>
-      <c r="C22" s="17">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
-        <v>0</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="17">
-        <v>9</v>
-      </c>
-      <c r="C23" s="17">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13">
-        <v>0</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="17">
-        <v>10</v>
-      </c>
-      <c r="C24" s="17">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13">
-        <v>0</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="17">
-        <v>11</v>
-      </c>
-      <c r="C25" s="17">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
-        <v>0</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="17">
-        <v>12</v>
-      </c>
-      <c r="C26" s="17">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13">
-        <v>0</v>
-      </c>
-      <c r="E26" s="13">
-        <v>0</v>
-      </c>
-      <c r="F26" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="17">
-        <v>13</v>
-      </c>
-      <c r="C27" s="17">
-        <v>0</v>
-      </c>
-      <c r="D27" s="13">
-        <v>0</v>
-      </c>
-      <c r="E27" s="13">
-        <v>0</v>
-      </c>
-      <c r="F27" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="17">
-        <v>14</v>
-      </c>
-      <c r="C28" s="17">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13">
-        <v>0</v>
-      </c>
-      <c r="E28" s="13">
-        <v>0</v>
-      </c>
-      <c r="F28" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="17">
-        <v>15</v>
-      </c>
-      <c r="C29" s="17">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13">
-        <v>0</v>
-      </c>
-      <c r="E29" s="13">
-        <v>0</v>
-      </c>
-      <c r="F29" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="17">
-        <v>16</v>
-      </c>
-      <c r="C30" s="17">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13">
-        <v>0</v>
-      </c>
-      <c r="E30" s="13">
-        <v>0</v>
-      </c>
-      <c r="F30" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="17">
-        <v>17</v>
-      </c>
-      <c r="C31" s="17">
-        <v>0</v>
-      </c>
-      <c r="D31" s="13">
-        <v>0</v>
-      </c>
-      <c r="E31" s="13">
-        <v>0</v>
-      </c>
-      <c r="F31" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="17">
-        <v>18</v>
-      </c>
-      <c r="C32" s="17">
-        <v>0</v>
-      </c>
-      <c r="D32" s="13">
-        <v>0</v>
-      </c>
-      <c r="E32" s="13">
-        <v>0</v>
-      </c>
-      <c r="F32" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="17">
-        <v>19</v>
-      </c>
-      <c r="C33" s="17">
-        <v>0</v>
-      </c>
-      <c r="D33" s="13">
-        <v>0</v>
-      </c>
-      <c r="E33" s="13">
-        <v>0</v>
-      </c>
-      <c r="F33" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="17">
-        <v>20</v>
-      </c>
-      <c r="C34" s="17">
-        <v>0</v>
-      </c>
-      <c r="D34" s="13">
-        <v>0</v>
-      </c>
-      <c r="E34" s="13">
-        <v>0</v>
-      </c>
-      <c r="F34" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="17">
-        <v>21</v>
-      </c>
-      <c r="C35" s="17">
-        <v>0</v>
-      </c>
-      <c r="D35" s="13">
-        <v>0</v>
-      </c>
-      <c r="E35" s="13">
-        <v>0</v>
-      </c>
-      <c r="F35" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="17">
-        <v>22</v>
-      </c>
-      <c r="C36" s="17">
-        <v>0</v>
-      </c>
-      <c r="D36" s="13">
-        <v>0</v>
-      </c>
-      <c r="E36" s="13">
-        <v>0</v>
-      </c>
-      <c r="F36" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="17">
-        <v>23</v>
-      </c>
-      <c r="C37" s="17">
-        <v>0</v>
-      </c>
-      <c r="D37" s="13">
-        <v>0</v>
-      </c>
-      <c r="E37" s="13">
-        <v>0</v>
-      </c>
-      <c r="F37" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="17">
-        <v>24</v>
-      </c>
-      <c r="C38" s="17">
-        <v>0</v>
-      </c>
-      <c r="D38" s="13">
-        <v>0</v>
-      </c>
-      <c r="E38" s="13">
-        <v>0</v>
-      </c>
-      <c r="F38" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="17">
-        <v>25</v>
-      </c>
-      <c r="C39" s="17">
-        <v>0</v>
-      </c>
-      <c r="D39" s="13">
-        <v>0</v>
-      </c>
-      <c r="E39" s="13">
-        <v>0</v>
-      </c>
-      <c r="F39" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="17">
-        <v>26</v>
-      </c>
-      <c r="C40" s="17">
-        <v>0</v>
-      </c>
-      <c r="D40" s="13">
-        <v>0</v>
-      </c>
-      <c r="E40" s="13">
-        <v>0</v>
-      </c>
-      <c r="F40" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="17">
-        <v>27</v>
-      </c>
-      <c r="C41" s="17">
-        <v>0</v>
-      </c>
-      <c r="D41" s="13">
-        <v>0</v>
-      </c>
-      <c r="E41" s="13">
-        <v>0</v>
-      </c>
-      <c r="F41" s="13">
+      <c r="C41" s="11">
+        <v>0</v>
+      </c>
+      <c r="D41" s="11">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="17">
+      <c r="B42" s="11">
         <v>28</v>
       </c>
-      <c r="C42" s="17">
-        <v>0</v>
-      </c>
-      <c r="D42" s="13">
-        <v>0</v>
-      </c>
-      <c r="E42" s="13">
-        <v>0</v>
-      </c>
-      <c r="F42" s="13">
+      <c r="C42" s="11">
+        <v>0</v>
+      </c>
+      <c r="D42" s="11">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11">
+        <v>0</v>
+      </c>
+      <c r="F42" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="17">
+      <c r="B43" s="11">
         <v>29</v>
       </c>
-      <c r="C43" s="17">
-        <v>0</v>
-      </c>
-      <c r="D43" s="13">
-        <v>0</v>
-      </c>
-      <c r="E43" s="13">
-        <v>0</v>
-      </c>
-      <c r="F43" s="13">
+      <c r="C43" s="11">
+        <v>0</v>
+      </c>
+      <c r="D43" s="11">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="17">
+      <c r="B44" s="11">
         <v>30</v>
       </c>
-      <c r="C44" s="17">
-        <v>0</v>
-      </c>
-      <c r="D44" s="13">
-        <v>0</v>
-      </c>
-      <c r="E44" s="13">
-        <v>0</v>
-      </c>
-      <c r="F44" s="13">
+      <c r="C44" s="11">
+        <v>0</v>
+      </c>
+      <c r="D44" s="11">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="17">
+      <c r="B45" s="11">
         <v>31</v>
       </c>
-      <c r="C45" s="17">
-        <v>0</v>
-      </c>
-      <c r="D45" s="13">
-        <v>0</v>
-      </c>
-      <c r="E45" s="13">
-        <v>0</v>
-      </c>
-      <c r="F45" s="13">
+      <c r="C45" s="11">
+        <v>0</v>
+      </c>
+      <c r="D45" s="11">
+        <v>0</v>
+      </c>
+      <c r="E45" s="11">
+        <v>0</v>
+      </c>
+      <c r="F45" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="17">
+      <c r="B46" s="11">
         <v>32</v>
       </c>
-      <c r="C46" s="17">
-        <v>0</v>
-      </c>
-      <c r="D46" s="13">
-        <v>0</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0</v>
-      </c>
-      <c r="F46" s="13">
+      <c r="C46" s="11">
+        <v>0</v>
+      </c>
+      <c r="D46" s="11">
+        <v>0</v>
+      </c>
+      <c r="E46" s="11">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="17">
+      <c r="B47" s="11">
         <v>33</v>
       </c>
-      <c r="C47" s="17">
-        <v>0</v>
-      </c>
-      <c r="D47" s="13">
-        <v>0</v>
-      </c>
-      <c r="E47" s="13">
-        <v>0</v>
-      </c>
-      <c r="F47" s="13">
+      <c r="C47" s="11">
+        <v>0</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="17">
+      <c r="B48" s="11">
         <v>34</v>
       </c>
-      <c r="C48" s="17">
-        <v>0</v>
-      </c>
-      <c r="D48" s="13">
-        <v>0</v>
-      </c>
-      <c r="E48" s="13">
-        <v>0</v>
-      </c>
-      <c r="F48" s="13">
+      <c r="C48" s="11">
+        <v>0</v>
+      </c>
+      <c r="D48" s="11">
+        <v>0</v>
+      </c>
+      <c r="E48" s="11">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="17">
+      <c r="B49" s="11">
         <v>35</v>
       </c>
-      <c r="C49" s="17">
-        <v>0</v>
-      </c>
-      <c r="D49" s="13">
-        <v>0</v>
-      </c>
-      <c r="E49" s="13">
-        <v>0</v>
-      </c>
-      <c r="F49" s="13">
+      <c r="C49" s="11">
+        <v>0</v>
+      </c>
+      <c r="D49" s="11">
+        <v>0</v>
+      </c>
+      <c r="E49" s="11">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="17">
+      <c r="B50" s="11">
         <v>36</v>
       </c>
-      <c r="C50" s="17">
-        <v>0</v>
-      </c>
-      <c r="D50" s="13">
-        <v>0</v>
-      </c>
-      <c r="E50" s="13">
-        <v>0</v>
-      </c>
-      <c r="F50" s="13">
+      <c r="C50" s="11">
+        <v>0</v>
+      </c>
+      <c r="D50" s="11">
+        <v>0</v>
+      </c>
+      <c r="E50" s="11">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="17">
+      <c r="B51" s="11">
         <v>37</v>
       </c>
-      <c r="C51" s="17">
-        <v>0</v>
-      </c>
-      <c r="D51" s="13">
-        <v>0</v>
-      </c>
-      <c r="E51" s="13">
-        <v>0</v>
-      </c>
-      <c r="F51" s="13">
+      <c r="C51" s="11">
+        <v>0</v>
+      </c>
+      <c r="D51" s="11">
+        <v>0</v>
+      </c>
+      <c r="E51" s="11">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="17">
+      <c r="B52" s="11">
         <v>38</v>
       </c>
-      <c r="C52" s="17">
-        <v>0</v>
-      </c>
-      <c r="D52" s="13">
-        <v>0</v>
-      </c>
-      <c r="E52" s="13">
-        <v>0</v>
-      </c>
-      <c r="F52" s="13">
+      <c r="C52" s="11">
+        <v>0</v>
+      </c>
+      <c r="D52" s="11">
+        <v>0</v>
+      </c>
+      <c r="E52" s="11">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="17">
+      <c r="B53" s="11">
         <v>39</v>
       </c>
-      <c r="C53" s="17">
-        <v>0</v>
-      </c>
-      <c r="D53" s="13">
-        <v>0</v>
-      </c>
-      <c r="E53" s="13">
-        <v>0</v>
-      </c>
-      <c r="F53" s="13">
+      <c r="C53" s="11">
+        <v>0</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0</v>
+      </c>
+      <c r="E53" s="11">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="17">
+      <c r="B54" s="11">
         <v>40</v>
       </c>
-      <c r="C54" s="17">
-        <v>0</v>
-      </c>
-      <c r="D54" s="13">
-        <v>0</v>
-      </c>
-      <c r="E54" s="13">
-        <v>0</v>
-      </c>
-      <c r="F54" s="13">
+      <c r="C54" s="11">
+        <v>0</v>
+      </c>
+      <c r="D54" s="11">
+        <v>0</v>
+      </c>
+      <c r="E54" s="11">
+        <v>0</v>
+      </c>
+      <c r="F54" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="17">
+      <c r="B55" s="11">
         <v>41</v>
       </c>
-      <c r="C55" s="17">
-        <v>0</v>
-      </c>
-      <c r="D55" s="13">
-        <v>0</v>
-      </c>
-      <c r="E55" s="13">
-        <v>0</v>
-      </c>
-      <c r="F55" s="13">
+      <c r="C55" s="11">
+        <v>0</v>
+      </c>
+      <c r="D55" s="11">
+        <v>0</v>
+      </c>
+      <c r="E55" s="11">
+        <v>0</v>
+      </c>
+      <c r="F55" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:6">
-      <c r="B56" s="17">
+      <c r="B56" s="11">
         <v>42</v>
       </c>
-      <c r="C56" s="17">
-        <v>0</v>
-      </c>
-      <c r="D56" s="13">
-        <v>0</v>
-      </c>
-      <c r="E56" s="13">
-        <v>0</v>
-      </c>
-      <c r="F56" s="13">
+      <c r="C56" s="11">
+        <v>0</v>
+      </c>
+      <c r="D56" s="11">
+        <v>0</v>
+      </c>
+      <c r="E56" s="11">
+        <v>0</v>
+      </c>
+      <c r="F56" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="17">
+      <c r="B57" s="11">
         <v>43</v>
       </c>
-      <c r="C57" s="17">
-        <v>0</v>
-      </c>
-      <c r="D57" s="13">
-        <v>0</v>
-      </c>
-      <c r="E57" s="13">
-        <v>0</v>
-      </c>
-      <c r="F57" s="13">
+      <c r="C57" s="11">
+        <v>0</v>
+      </c>
+      <c r="D57" s="11">
+        <v>0</v>
+      </c>
+      <c r="E57" s="11">
+        <v>0</v>
+      </c>
+      <c r="F57" s="11">
         <v>0.0155038759689922</v>
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="17">
+      <c r="B58" s="11">
         <v>44</v>
       </c>
-      <c r="C58" s="17">
-        <v>0</v>
-      </c>
-      <c r="D58" s="13">
-        <v>0</v>
-      </c>
-      <c r="E58" s="13">
-        <v>0</v>
-      </c>
-      <c r="F58" s="13">
+      <c r="C58" s="11">
+        <v>0</v>
+      </c>
+      <c r="D58" s="11">
+        <v>0</v>
+      </c>
+      <c r="E58" s="11">
+        <v>0</v>
+      </c>
+      <c r="F58" s="11">
         <v>0.0151515151515152</v>
       </c>
     </row>
     <row r="59" spans="2:6">
-      <c r="B59" s="17">
+      <c r="B59" s="11">
         <v>45</v>
       </c>
-      <c r="C59" s="17">
-        <v>0</v>
-      </c>
-      <c r="D59" s="13">
-        <v>0</v>
-      </c>
-      <c r="E59" s="13">
-        <v>0</v>
-      </c>
-      <c r="F59" s="13">
+      <c r="C59" s="11">
+        <v>0</v>
+      </c>
+      <c r="D59" s="11">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11">
+        <v>0</v>
+      </c>
+      <c r="F59" s="11">
         <v>0.0222222222222222</v>
       </c>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="17">
+      <c r="B60" s="11">
         <v>46</v>
       </c>
-      <c r="C60" s="17">
-        <v>0</v>
-      </c>
-      <c r="D60" s="13">
-        <v>0</v>
-      </c>
-      <c r="E60" s="13">
+      <c r="C60" s="11">
+        <v>0</v>
+      </c>
+      <c r="D60" s="11">
+        <v>0</v>
+      </c>
+      <c r="E60" s="11">
         <v>0.0217391304347826</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="11">
         <v>0.0289855072463768</v>
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="17">
+      <c r="B61" s="11">
         <v>47</v>
       </c>
-      <c r="C61" s="17">
-        <v>0</v>
-      </c>
-      <c r="D61" s="13">
-        <v>0</v>
-      </c>
-      <c r="E61" s="13">
+      <c r="C61" s="11">
+        <v>0</v>
+      </c>
+      <c r="D61" s="11">
+        <v>0</v>
+      </c>
+      <c r="E61" s="11">
         <v>0.0212765957446809</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="11">
         <v>0.0354609929078014</v>
       </c>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="17">
+      <c r="B62" s="11">
         <v>48</v>
       </c>
-      <c r="C62" s="17">
-        <v>0</v>
-      </c>
-      <c r="D62" s="13">
-        <v>0</v>
-      </c>
-      <c r="E62" s="13">
+      <c r="C62" s="11">
+        <v>0</v>
+      </c>
+      <c r="D62" s="11">
+        <v>0</v>
+      </c>
+      <c r="E62" s="11">
         <v>0.032258064516129</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62" s="11">
         <v>0.0347222222222222</v>
       </c>
     </row>
     <row r="63" spans="2:6">
-      <c r="B63" s="17">
+      <c r="B63" s="11">
         <v>49</v>
       </c>
-      <c r="C63" s="17">
-        <v>0</v>
-      </c>
-      <c r="D63" s="13">
-        <v>0</v>
-      </c>
-      <c r="E63" s="13">
+      <c r="C63" s="11">
+        <v>0</v>
+      </c>
+      <c r="D63" s="11">
+        <v>0</v>
+      </c>
+      <c r="E63" s="11">
         <v>0.0327868852459016</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="11">
         <v>0.0340136054421769</v>
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="17">
+      <c r="B64" s="11">
         <v>50</v>
       </c>
-      <c r="C64" s="17">
-        <v>0</v>
-      </c>
-      <c r="D64" s="13">
-        <v>0</v>
-      </c>
-      <c r="E64" s="13">
+      <c r="C64" s="11">
+        <v>0</v>
+      </c>
+      <c r="D64" s="11">
+        <v>0</v>
+      </c>
+      <c r="E64" s="11">
         <v>0.0333333333333333</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="11">
         <v>0.04</v>
       </c>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="17">
+      <c r="B65" s="11">
         <v>51</v>
       </c>
-      <c r="C65" s="17">
-        <v>0</v>
-      </c>
-      <c r="D65" s="13">
-        <v>0</v>
-      </c>
-      <c r="E65" s="13">
+      <c r="C65" s="11">
+        <v>0</v>
+      </c>
+      <c r="D65" s="11">
+        <v>0</v>
+      </c>
+      <c r="E65" s="11">
         <v>0.0338983050847458</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="11">
         <v>0.0392156862745098</v>
       </c>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="17">
+      <c r="B66" s="11">
         <v>52</v>
       </c>
-      <c r="C66" s="17">
-        <v>0</v>
-      </c>
-      <c r="D66" s="13">
-        <v>0</v>
-      </c>
-      <c r="E66" s="13">
+      <c r="C66" s="11">
+        <v>0</v>
+      </c>
+      <c r="D66" s="11">
+        <v>0</v>
+      </c>
+      <c r="E66" s="11">
         <v>0.0344827586206897</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="11">
         <v>0.0384615384615385</v>
       </c>
     </row>
     <row r="67" spans="2:8">
-      <c r="B67" s="17">
+      <c r="B67" s="11">
         <v>53</v>
       </c>
-      <c r="C67" s="17">
-        <v>0</v>
-      </c>
-      <c r="D67" s="13">
-        <v>0</v>
-      </c>
-      <c r="E67" s="13">
+      <c r="C67" s="11">
+        <v>0</v>
+      </c>
+      <c r="D67" s="11">
+        <v>0</v>
+      </c>
+      <c r="E67" s="11">
         <v>0.0350877192982456</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="11">
         <v>0.0377358490566038</v>
       </c>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="17">
+      <c r="B68" s="11">
         <v>54</v>
       </c>
-      <c r="C68" s="17">
-        <v>0</v>
-      </c>
-      <c r="D68" s="13">
+      <c r="C68" s="11">
+        <v>0</v>
+      </c>
+      <c r="D68" s="11">
         <v>0.00617283950617284</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="11">
         <v>0.0357142857142857</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="11">
         <v>0.037037037037037</v>
       </c>
     </row>
     <row r="69" spans="2:8">
-      <c r="B69" s="17">
+      <c r="B69" s="11">
         <v>55</v>
       </c>
-      <c r="C69" s="17">
-        <v>0</v>
-      </c>
-      <c r="D69" s="13">
+      <c r="C69" s="11">
+        <v>0</v>
+      </c>
+      <c r="D69" s="11">
         <v>0.00606060606060606</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="11">
         <v>0.0363636363636364</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="11">
         <v>0.0424242424242424</v>
       </c>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="17">
+      <c r="B70" s="11">
         <v>56</v>
       </c>
-      <c r="C70" s="17">
-        <v>0</v>
-      </c>
-      <c r="D70" s="13">
+      <c r="C70" s="11">
+        <v>0</v>
+      </c>
+      <c r="D70" s="11">
         <v>0.0163934426229508</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="11">
         <v>0.037037037037037</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="11">
         <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="71" spans="2:8">
-      <c r="B71" s="17">
+      <c r="B71" s="11">
         <v>57</v>
       </c>
-      <c r="C71" s="17">
-        <v>0</v>
-      </c>
-      <c r="D71" s="13">
+      <c r="C71" s="11">
+        <v>0</v>
+      </c>
+      <c r="D71" s="11">
         <v>0.0166666666666667</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="11">
         <v>0.0377358490566038</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="11">
         <v>0.0409356725146199</v>
       </c>
     </row>
     <row r="72" spans="2:8">
-      <c r="B72" s="17">
+      <c r="B72" s="11">
         <v>58</v>
       </c>
-      <c r="C72" s="17">
-        <v>0</v>
-      </c>
-      <c r="D72" s="13">
+      <c r="C72" s="11">
+        <v>0</v>
+      </c>
+      <c r="D72" s="11">
         <v>0.0169491525423729</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="11">
         <v>0.0384615384615385</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="11">
         <v>0.0459770114942529</v>
       </c>
     </row>
     <row r="73" spans="2:8">
-      <c r="B73" s="17">
+      <c r="B73" s="11">
         <v>59</v>
       </c>
-      <c r="C73" s="17">
-        <v>0</v>
-      </c>
-      <c r="D73" s="13">
+      <c r="C73" s="11">
+        <v>0</v>
+      </c>
+      <c r="D73" s="11">
         <v>0.0172413793103448</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="11">
         <v>0.0392156862745098</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73" s="11">
         <v>0.0451977401129944</v>
       </c>
     </row>
     <row r="74" spans="2:8">
-      <c r="B74" s="17">
+      <c r="B74" s="11">
         <v>60</v>
       </c>
-      <c r="C74" s="17">
-        <v>0</v>
-      </c>
-      <c r="D74" s="13">
+      <c r="C74" s="11">
+        <v>0</v>
+      </c>
+      <c r="D74" s="11">
         <v>0.0175438596491228</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="11">
         <v>0.04</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="11">
         <v>0.05</v>
       </c>
     </row>
     <row r="75" spans="2:8">
-      <c r="B75" s="17">
+      <c r="B75" s="11">
         <v>61</v>
       </c>
-      <c r="C75" s="17">
-        <v>0</v>
-      </c>
-      <c r="D75" s="13">
+      <c r="C75" s="11">
+        <v>0</v>
+      </c>
+      <c r="D75" s="11">
         <v>0.0178571428571429</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="11">
         <v>0.0408163265306122</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75" s="11">
         <v>0.0491803278688525</v>
       </c>
     </row>
     <row r="76" spans="2:8">
-      <c r="B76" s="17">
+      <c r="B76" s="11">
         <v>62</v>
       </c>
-      <c r="C76" s="17">
-        <v>0</v>
-      </c>
-      <c r="D76" s="13">
+      <c r="C76" s="11">
+        <v>0</v>
+      </c>
+      <c r="D76" s="11">
         <v>0.021505376344086</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="11">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="11">
         <v>0.0483870967741935</v>
       </c>
     </row>
     <row r="77" spans="2:8">
-      <c r="B77" s="17">
+      <c r="B77" s="11">
         <v>63</v>
       </c>
-      <c r="C77" s="17">
-        <v>0</v>
-      </c>
-      <c r="D77" s="13">
+      <c r="C77" s="11">
+        <v>0</v>
+      </c>
+      <c r="D77" s="11">
         <v>0.0211640211640212</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="11">
         <v>0.0476190476190476</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="11">
         <v>0.0476190476190476</v>
       </c>
     </row>
     <row r="78" spans="2:8">
-      <c r="B78" s="17">
+      <c r="B78" s="11">
         <v>64</v>
       </c>
-      <c r="C78" s="17">
-        <v>0</v>
-      </c>
-      <c r="D78" s="13">
+      <c r="C78" s="11">
+        <v>0</v>
+      </c>
+      <c r="D78" s="11">
         <v>0.03125</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="11">
         <v>0.0625</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="11">
         <v>0.0520833333333333</v>
       </c>
     </row>
     <row r="79" spans="2:8">
-      <c r="B79" s="17">
+      <c r="B79" s="11">
         <v>65</v>
       </c>
-      <c r="C79" s="17">
-        <v>0</v>
-      </c>
-      <c r="D79" s="13">
+      <c r="C79" s="11">
+        <v>0</v>
+      </c>
+      <c r="D79" s="11">
         <v>0.0307692307692308</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="11">
         <v>0.0769230769230769</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="11">
         <v>0.0615384615384615</v>
       </c>
     </row>
     <row r="80" spans="2:8">
-      <c r="B80" s="17">
+      <c r="B80" s="11">
         <v>66</v>
       </c>
-      <c r="C80" s="17">
-        <v>0</v>
-      </c>
-      <c r="D80" s="13">
+      <c r="C80" s="11">
+        <v>0</v>
+      </c>
+      <c r="D80" s="11">
         <v>0.0303030303030303</v>
       </c>
       <c r="E80" s="7">
         <v>0.0857142857142857</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80" s="11">
         <v>0.0656565656565656</v>
       </c>
-      <c r="H80" s="18"/>
+      <c r="H80" s="12"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="17">
+      <c r="B81" s="11">
         <v>67</v>
       </c>
-      <c r="C81" s="17">
-        <v>0</v>
-      </c>
-      <c r="D81" s="13">
+      <c r="C81" s="11">
+        <v>0</v>
+      </c>
+      <c r="D81" s="11">
         <v>0.0398009950248756</v>
       </c>
       <c r="E81" s="7">
         <v>0.0869565217391304</v>
       </c>
-      <c r="F81" s="13">
+      <c r="F81" s="11">
         <v>0.0646766169154229</v>
       </c>
     </row>
     <row r="82" spans="2:6">
-      <c r="B82" s="17">
+      <c r="B82" s="11">
         <v>68</v>
       </c>
-      <c r="C82" s="17">
-        <v>0</v>
-      </c>
-      <c r="D82" s="13">
+      <c r="C82" s="11">
+        <v>0</v>
+      </c>
+      <c r="D82" s="11">
         <v>0.0392156862745098</v>
       </c>
       <c r="E82" s="7">
         <v>0.0882352941176471</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="11">
         <v>0.0686274509803921</v>
       </c>
     </row>
     <row r="83" spans="2:6">
-      <c r="B83" s="17">
+      <c r="B83" s="11">
         <v>69</v>
       </c>
-      <c r="C83" s="17">
-        <v>0</v>
-      </c>
-      <c r="D83" s="13">
+      <c r="C83" s="11">
+        <v>0</v>
+      </c>
+      <c r="D83" s="11">
         <v>0.0483091787439614</v>
       </c>
       <c r="E83" s="7">
         <v>0.0885416666666667</v>
       </c>
-      <c r="F83" s="13">
+      <c r="F83" s="11">
         <v>0.0821256038647343</v>
       </c>
     </row>
     <row r="84" spans="2:6">
-      <c r="B84" s="17">
+      <c r="B84" s="11">
         <v>70</v>
       </c>
-      <c r="C84" s="17">
-        <v>0</v>
-      </c>
-      <c r="D84" s="13">
+      <c r="C84" s="11">
+        <v>0</v>
+      </c>
+      <c r="D84" s="11">
         <v>0.0523809523809524</v>
       </c>
       <c r="E84" s="7">
         <v>0.0886075949367089</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="11">
         <v>0.0857142857142857</v>
       </c>
     </row>
     <row r="85" spans="2:6">
-      <c r="B85" s="17">
+      <c r="B85" s="11">
         <v>71</v>
       </c>
-      <c r="C85" s="17">
-        <v>0</v>
-      </c>
-      <c r="D85" s="13">
+      <c r="C85" s="11">
+        <v>0</v>
+      </c>
+      <c r="D85" s="11">
         <v>0.0601851851851852</v>
       </c>
       <c r="E85" s="7">
         <v>0.0895522388059701</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85" s="11">
         <v>0.0892018779342723</v>
       </c>
     </row>
     <row r="86" spans="2:6">
-      <c r="B86" s="17">
+      <c r="B86" s="11">
         <v>72</v>
       </c>
-      <c r="C86" s="17">
-        <v>0</v>
-      </c>
-      <c r="D86" s="13">
+      <c r="C86" s="11">
+        <v>0</v>
+      </c>
+      <c r="D86" s="11">
         <v>0.0610328638497653</v>
       </c>
       <c r="E86" s="7">
         <v>0.0897435897435897</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86" s="11">
         <v>0.087962962962963</v>
       </c>
     </row>
     <row r="87" spans="2:6">
-      <c r="B87" s="17">
+      <c r="B87" s="11">
         <v>73</v>
       </c>
-      <c r="C87" s="17">
-        <v>0</v>
-      </c>
-      <c r="D87" s="13">
+      <c r="C87" s="11">
+        <v>0</v>
+      </c>
+      <c r="D87" s="11">
         <v>0.0639269406392694</v>
       </c>
       <c r="E87" s="7">
         <v>0.0909090909090909</v>
       </c>
-      <c r="F87" s="13">
+      <c r="F87" s="11">
         <v>0.0867579908675799</v>
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="17">
+      <c r="B88" s="11">
         <v>74</v>
       </c>
-      <c r="C88" s="17">
-        <v>0</v>
-      </c>
-      <c r="D88" s="13">
+      <c r="C88" s="11">
+        <v>0</v>
+      </c>
+      <c r="D88" s="11">
         <v>0.0675675675675676</v>
       </c>
       <c r="E88" s="7">
         <v>0.0921052631578947</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="11">
         <v>0.0990990990990991</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="17">
+      <c r="B89" s="11">
         <v>75</v>
       </c>
-      <c r="C89" s="17">
+      <c r="C89" s="11">
         <v>0.00432900432900433</v>
       </c>
-      <c r="D89" s="13">
+      <c r="D89" s="11">
         <v>0.0745614035087719</v>
       </c>
       <c r="E89" s="7">
         <v>0.0933333333333333</v>
       </c>
-      <c r="F89" s="13">
+      <c r="F89" s="11">
         <v>0.106666666666667</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="17">
+      <c r="B90" s="11">
         <v>76</v>
       </c>
-      <c r="C90" s="17">
+      <c r="C90" s="11">
         <v>0.0043859649122807</v>
       </c>
-      <c r="D90" s="13">
+      <c r="D90" s="11">
         <v>0.0755555555555556</v>
       </c>
       <c r="E90" s="7">
         <v>0.0945945945945946</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="11">
         <v>0.114035087719298</v>
       </c>
     </row>
     <row r="91" spans="2:6">
-      <c r="B91" s="17">
+      <c r="B91" s="11">
         <v>77</v>
       </c>
-      <c r="C91" s="17">
+      <c r="C91" s="11">
         <v>0.00444444444444444</v>
       </c>
-      <c r="D91" s="13">
+      <c r="D91" s="11">
         <v>0.0865800865800866</v>
       </c>
       <c r="E91" s="7">
         <v>0.0958904109589041</v>
       </c>
-      <c r="F91" s="13">
+      <c r="F91" s="11">
         <v>0.112554112554113</v>
       </c>
     </row>
     <row r="92" spans="2:6">
-      <c r="B92" s="17">
+      <c r="B92" s="11">
         <v>78</v>
       </c>
-      <c r="C92" s="17">
+      <c r="C92" s="11">
         <v>0.00854700854700855</v>
       </c>
-      <c r="D92" s="13">
+      <c r="D92" s="11">
         <v>0.0897435897435898</v>
       </c>
       <c r="E92" s="7">
         <v>0.0972222222222222</v>
       </c>
-      <c r="F92" s="13">
+      <c r="F92" s="11">
         <v>0.115384615384615</v>
       </c>
     </row>
     <row r="93" spans="2:6">
-      <c r="B93" s="17">
+      <c r="B93" s="11">
         <v>79</v>
       </c>
-      <c r="C93" s="17">
+      <c r="C93" s="11">
         <v>0.0126582278481013</v>
       </c>
-      <c r="D93" s="13">
+      <c r="D93" s="11">
         <v>0.0928270042194093</v>
       </c>
       <c r="E93" s="7">
         <v>0.0985915492957746</v>
       </c>
-      <c r="F93" s="13">
+      <c r="F93" s="11">
         <v>0.113924050632911</v>
       </c>
     </row>
     <row r="94" spans="2:6">
-      <c r="B94" s="17">
+      <c r="B94" s="11">
         <v>80</v>
       </c>
-      <c r="C94" s="17">
+      <c r="C94" s="11">
         <v>0.016260162601626</v>
       </c>
-      <c r="D94" s="13">
+      <c r="D94" s="11">
         <v>0.0912698412698413</v>
       </c>
-      <c r="E94" s="13">
+      <c r="E94" s="11">
         <v>0.1</v>
       </c>
-      <c r="F94" s="13">
+      <c r="F94" s="11">
         <v>0.120833333333333</v>
       </c>
     </row>
     <row r="95" spans="2:6">
-      <c r="B95" s="17">
+      <c r="B95" s="11">
         <v>81</v>
       </c>
-      <c r="C95" s="17">
+      <c r="C95" s="11">
         <v>0.0164609053497942</v>
       </c>
-      <c r="D95" s="13">
+      <c r="D95" s="11">
         <v>0.0923694779116466</v>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="11">
         <v>0.0987654320987654</v>
       </c>
-      <c r="F95" s="13">
+      <c r="F95" s="11">
         <v>0.123456790123457</v>
       </c>
     </row>
     <row r="96" spans="2:6">
-      <c r="B96" s="17">
+      <c r="B96" s="11">
         <v>82</v>
       </c>
-      <c r="C96" s="17">
+      <c r="C96" s="11">
         <v>0.0166666666666667</v>
       </c>
-      <c r="D96" s="13">
+      <c r="D96" s="11">
         <v>0.0934959349593496</v>
       </c>
-      <c r="E96" s="13">
+      <c r="E96" s="11">
         <v>0.0975609756097561</v>
       </c>
-      <c r="F96" s="13">
+      <c r="F96" s="11">
         <v>0.126016260162602</v>
       </c>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="17">
+      <c r="B97" s="11">
         <v>83</v>
       </c>
-      <c r="C97" s="17">
+      <c r="C97" s="11">
         <v>0.0200803212851406</v>
       </c>
-      <c r="D97" s="13">
+      <c r="D97" s="11">
         <v>0.0946502057613169</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="11">
         <v>0.108433734939759</v>
       </c>
-      <c r="F97" s="13">
+      <c r="F97" s="11">
         <v>0.124497991967871</v>
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="17">
+      <c r="B98" s="11">
         <v>84</v>
       </c>
-      <c r="C98" s="17">
+      <c r="C98" s="11">
         <v>0.0235294117647059</v>
       </c>
-      <c r="D98" s="13">
+      <c r="D98" s="11">
         <v>0.0958333333333333</v>
       </c>
-      <c r="E98" s="13">
+      <c r="E98" s="11">
         <v>0.119047619047619</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="11">
         <v>0.130952380952381</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="17">
+      <c r="B99" s="11">
         <v>85</v>
       </c>
-      <c r="C99" s="17">
+      <c r="C99" s="11">
         <v>0.0238095238095238</v>
       </c>
-      <c r="D99" s="13">
+      <c r="D99" s="11">
         <v>0.101960784313726</v>
       </c>
-      <c r="E99" s="13">
+      <c r="E99" s="11">
         <v>0.117647058823529</v>
       </c>
-      <c r="F99" s="13">
+      <c r="F99" s="11">
         <v>0.137254901960784</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="17">
+      <c r="B100" s="11">
         <v>86</v>
       </c>
-      <c r="C100" s="17">
+      <c r="C100" s="11">
         <v>0.0268199233716475</v>
       </c>
-      <c r="D100" s="13">
+      <c r="D100" s="11">
         <v>0.108527131782946</v>
       </c>
-      <c r="E100" s="13">
+      <c r="E100" s="11">
         <v>0.127906976744186</v>
       </c>
-      <c r="F100" s="13">
+      <c r="F100" s="11">
         <v>0.143410852713178</v>
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="17">
+      <c r="B101" s="11">
         <v>87</v>
       </c>
-      <c r="C101" s="17">
+      <c r="C101" s="11">
         <v>0.0271317829457364</v>
       </c>
-      <c r="D101" s="13">
+      <c r="D101" s="11">
         <v>0.111111111111111</v>
       </c>
-      <c r="E101" s="13">
+      <c r="E101" s="11">
         <v>0.126436781609195</v>
       </c>
-      <c r="F101" s="13">
+      <c r="F101" s="11">
         <v>0.149425287356322</v>
       </c>
     </row>
     <row r="102" spans="2:6">
-      <c r="B102" s="17">
+      <c r="B102" s="11">
         <v>88</v>
       </c>
-      <c r="C102" s="17">
+      <c r="C102" s="11">
         <v>0.0337078651685393</v>
       </c>
-      <c r="D102" s="13">
+      <c r="D102" s="11">
         <v>0.111111111111111</v>
       </c>
-      <c r="E102" s="13">
+      <c r="E102" s="11">
         <v>0.125</v>
       </c>
-      <c r="F102" s="13">
+      <c r="F102" s="11">
         <v>0.15530303030303</v>
       </c>
     </row>
     <row r="103" spans="2:6">
-      <c r="B103" s="17">
+      <c r="B103" s="11">
         <v>89</v>
       </c>
-      <c r="C103" s="17">
+      <c r="C103" s="11">
         <v>0.0340909090909091</v>
       </c>
-      <c r="D103" s="13">
+      <c r="D103" s="11">
         <v>0.112359550561798</v>
       </c>
-      <c r="E103" s="13">
+      <c r="E103" s="11">
         <v>0.123595505617978</v>
       </c>
-      <c r="F103" s="13">
+      <c r="F103" s="11">
         <v>0.157303370786517</v>
       </c>
     </row>
     <row r="104" spans="2:6">
-      <c r="B104" s="17">
+      <c r="B104" s="11">
         <v>90</v>
       </c>
-      <c r="C104" s="17">
+      <c r="C104" s="11">
         <v>0.037037037037037</v>
       </c>
-      <c r="D104" s="13">
+      <c r="D104" s="11">
         <v>0.113636363636364</v>
       </c>
-      <c r="E104" s="13">
+      <c r="E104" s="11">
         <v>0.122222222222222</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104" s="11">
         <v>0.155555555555556</v>
       </c>
     </row>
     <row r="105" spans="2:6">
-      <c r="B105" s="17">
+      <c r="B105" s="11">
         <v>91</v>
       </c>
-      <c r="C105" s="17">
+      <c r="C105" s="11">
         <v>0.0402930402930403</v>
       </c>
-      <c r="D105" s="13">
+      <c r="D105" s="11">
         <v>0.117216117216117</v>
       </c>
-      <c r="E105" s="13">
+      <c r="E105" s="11">
         <v>0.120879120879121</v>
       </c>
-      <c r="F105" s="13">
+      <c r="F105" s="11">
         <v>0.161172161172161</v>
       </c>
     </row>
     <row r="106" spans="2:6">
-      <c r="B106" s="17">
+      <c r="B106" s="11">
         <v>92</v>
       </c>
-      <c r="C106" s="17">
+      <c r="C106" s="11">
         <v>0.0434782608695652</v>
       </c>
-      <c r="D106" s="13">
+      <c r="D106" s="11">
         <v>0.123188405797101</v>
       </c>
-      <c r="E106" s="13">
+      <c r="E106" s="11">
         <v>0.119565217391304</v>
       </c>
-      <c r="F106" s="13">
+      <c r="F106" s="11">
         <v>0.16304347826087</v>
       </c>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="17">
+      <c r="B107" s="11">
         <v>93</v>
       </c>
-      <c r="C107" s="17">
+      <c r="C107" s="11">
         <v>0.046594982078853</v>
       </c>
-      <c r="D107" s="13">
+      <c r="D107" s="11">
         <v>0.125448028673835</v>
       </c>
-      <c r="E107" s="13">
+      <c r="E107" s="11">
         <v>0.129032258064516</v>
       </c>
-      <c r="F107" s="13">
+      <c r="F107" s="11">
         <v>0.164874551971326</v>
       </c>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="17">
+      <c r="B108" s="11">
         <v>94</v>
       </c>
-      <c r="C108" s="17">
+      <c r="C108" s="11">
         <v>0.049645390070922</v>
       </c>
-      <c r="D108" s="13">
+      <c r="D108" s="11">
         <v>0.134751773049645</v>
       </c>
-      <c r="E108" s="13">
+      <c r="E108" s="11">
         <v>0.127659574468085</v>
       </c>
-      <c r="F108" s="13">
+      <c r="F108" s="11">
         <v>0.173758865248227</v>
       </c>
     </row>
     <row r="109" spans="2:6">
-      <c r="B109" s="17">
+      <c r="B109" s="11">
         <v>95</v>
       </c>
-      <c r="C109" s="17">
+      <c r="C109" s="11">
         <v>0.056140350877193</v>
       </c>
-      <c r="D109" s="13">
+      <c r="D109" s="11">
         <v>0.138888888888889</v>
       </c>
-      <c r="E109" s="13">
+      <c r="E109" s="11">
         <v>0.136842105263158</v>
       </c>
-      <c r="F109" s="13">
+      <c r="F109" s="11">
         <v>0.178947368421053</v>
       </c>
     </row>
     <row r="110" spans="2:6">
-      <c r="B110" s="17">
+      <c r="B110" s="11">
         <v>96</v>
       </c>
-      <c r="C110" s="17">
+      <c r="C110" s="11">
         <v>0.0625</v>
       </c>
-      <c r="D110" s="13">
+      <c r="D110" s="11">
         <v>0.140350877192982</v>
       </c>
-      <c r="E110" s="13">
+      <c r="E110" s="11">
         <v>0.145833333333333</v>
       </c>
-      <c r="F110" s="13">
+      <c r="F110" s="11">
         <v>0.1875</v>
       </c>
     </row>
     <row r="111" spans="2:6">
-      <c r="B111" s="17">
+      <c r="B111" s="11">
         <v>97</v>
       </c>
-      <c r="C111" s="17">
+      <c r="C111" s="11">
         <v>0.0707070707070707</v>
       </c>
-      <c r="D111" s="13">
+      <c r="D111" s="11">
         <v>0.140893470790378</v>
       </c>
-      <c r="E111" s="13">
+      <c r="E111" s="11">
         <v>0.154639175257732</v>
       </c>
-      <c r="F111" s="13">
+      <c r="F111" s="11">
         <v>0.189003436426117</v>
       </c>
     </row>
     <row r="112" spans="2:6">
-      <c r="B112" s="17">
+      <c r="B112" s="11">
         <v>98</v>
       </c>
-      <c r="C112" s="17">
+      <c r="C112" s="11">
         <v>0.0714285714285714</v>
       </c>
-      <c r="D112" s="13">
+      <c r="D112" s="11">
         <v>0.146258503401361</v>
       </c>
-      <c r="E112" s="13">
+      <c r="E112" s="11">
         <v>0.163265306122449</v>
       </c>
-      <c r="F112" s="13">
-        <f ca="1">COUNTIF(C$7:$AA112,0)/ROWS(C$7:$AA112)</f>
-        <v>0.195876288659794</v>
+      <c r="F112" s="11">
+        <v>0.195876289</v>
       </c>
     </row>
     <row r="113" spans="2:6">
-      <c r="B113" s="17">
+      <c r="B113" s="11">
         <v>99</v>
       </c>
-      <c r="C113" s="17">
+      <c r="C113" s="11">
         <v>0.0721649484536083</v>
       </c>
-      <c r="D113" s="13">
+      <c r="D113" s="11">
         <v>0.151515151515152</v>
       </c>
-      <c r="E113" s="13">
+      <c r="E113" s="11">
         <v>0.171717171717172</v>
       </c>
-      <c r="F113" s="13">
+      <c r="F113" s="11">
         <v>0.197278911564626</v>
       </c>
     </row>
     <row r="114" spans="2:6">
-      <c r="B114" s="17">
+      <c r="B114" s="11">
         <v>100</v>
       </c>
-      <c r="C114" s="17">
+      <c r="C114" s="11">
         <v>0.0733333333333333</v>
       </c>
-      <c r="D114" s="13">
+      <c r="D114" s="11">
         <v>0.156666666666667</v>
       </c>
-      <c r="E114" s="13">
+      <c r="E114" s="11">
         <v>0.18</v>
       </c>
-      <c r="F114" s="13">
-        <f ca="1">COUNTIF(C$7:$AA114,0)/ROWS(C$7:$AA114)</f>
-        <v>0.197916666666667</v>
+      <c r="F114" s="11">
+        <v>0.197916667</v>
       </c>
     </row>
   </sheetData>
@@ -10144,7 +10121,7 @@
         <v>0.0454545454545455</v>
       </c>
       <c r="P71" s="5">
-        <f t="shared" ref="P71:P102" si="9">AVERAGE(M71:O71)</f>
+        <f t="shared" ref="P71:P105" si="9">AVERAGE(M71:O71)</f>
         <v>0.0303030303030303</v>
       </c>
       <c r="R71" s="5">
@@ -10169,7 +10146,7 @@
         <v>0.0909090909090909</v>
       </c>
       <c r="X71" s="5">
-        <f t="shared" ref="X71:X102" si="10">AVERAGE(U71:W71)</f>
+        <f t="shared" ref="X71:X105" si="10">AVERAGE(U71:W71)</f>
         <v>0.101010101010101</v>
       </c>
       <c r="Z71" s="5">
@@ -10194,7 +10171,7 @@
         <v>0.0606060606060606</v>
       </c>
       <c r="AF71" s="5">
-        <f t="shared" ref="AF71:AF102" si="11">AVERAGE(AC71:AE71)</f>
+        <f t="shared" ref="AF71:AF105" si="11">AVERAGE(AC71:AE71)</f>
         <v>0.0656565656565656</v>
       </c>
     </row>
@@ -13504,7 +13481,7 @@
         <v>0.153061224489796</v>
       </c>
       <c r="P103" s="5">
-        <f>AVERAGE(M103:O103)</f>
+        <f t="shared" si="9"/>
         <v>0.146258503401361</v>
       </c>
       <c r="R103" s="5">
@@ -13529,7 +13506,7 @@
         <v>0.255102040816327</v>
       </c>
       <c r="X103" s="5">
-        <f>AVERAGE(U103:W103)</f>
+        <f t="shared" si="10"/>
         <v>0.214285714285714</v>
       </c>
       <c r="Z103" s="5">
@@ -13554,7 +13531,7 @@
         <v>0.23469387755102</v>
       </c>
       <c r="AF103" s="5">
-        <f>AVERAGE(AC103:AE103)</f>
+        <f t="shared" si="11"/>
         <v>0.197278911564626</v>
       </c>
     </row>
@@ -13609,7 +13586,7 @@
         <v>0.151515151515152</v>
       </c>
       <c r="P104" s="5">
-        <f>AVERAGE(M104:O104)</f>
+        <f t="shared" si="9"/>
         <v>0.151515151515152</v>
       </c>
       <c r="R104" s="5">
@@ -13634,7 +13611,7 @@
         <v>0.252525252525253</v>
       </c>
       <c r="X104" s="5">
-        <f>AVERAGE(U104:W104)</f>
+        <f t="shared" si="10"/>
         <v>0.218855218855219</v>
       </c>
       <c r="Z104" s="5">
@@ -13659,7 +13636,7 @@
         <v>0.232323232323232</v>
       </c>
       <c r="AF104" s="5">
-        <f>AVERAGE(AC104:AE104)</f>
+        <f t="shared" si="11"/>
         <v>0.202020202020202</v>
       </c>
     </row>
@@ -13714,7 +13691,7 @@
         <v>0.15</v>
       </c>
       <c r="P105" s="5">
-        <f>AVERAGE(M105:O105)</f>
+        <f t="shared" si="9"/>
         <v>0.156666666666667</v>
       </c>
       <c r="R105" s="5">
@@ -13739,7 +13716,7 @@
         <v>0.26</v>
       </c>
       <c r="X105" s="5">
-        <f>AVERAGE(U105:W105)</f>
+        <f t="shared" si="10"/>
         <v>0.226666666666667</v>
       </c>
       <c r="Z105" s="5">
@@ -13764,7 +13741,7 @@
         <v>0.24</v>
       </c>
       <c r="AF105" s="5">
-        <f>AVERAGE(AC105:AE105)</f>
+        <f t="shared" si="11"/>
         <v>0.203333333333333</v>
       </c>
     </row>
